--- a/Modelo - Control Compromisos para Ventas (FECHA).xlsx
+++ b/Modelo - Control Compromisos para Ventas (FECHA).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e2868b21c6fa256/Documents/1 - CONTROLES DE GRUPO_METHODUS/16 - ADMINIST GM/09-PLAN METAS X RESPONSABLES/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="8_{B1ED4FEC-DA4F-4FDF-81C2-29662D724100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73F21751-4ED9-460E-8E7D-D71CC417528D}"/>
+  <xr:revisionPtr revIDLastSave="34" documentId="8_{B1ED4FEC-DA4F-4FDF-81C2-29662D724100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{711B0E7D-8FAB-40DD-A0F9-347995ECF200}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{90560D21-195F-411D-888C-C360E96F9F1B}"/>
   </bookViews>
@@ -25,12 +25,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Cliente</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fecha </t>
   </si>
   <si>
     <t>1o. Contacto</t>
@@ -39,49 +36,31 @@
     <t>Ultimo Contacto</t>
   </si>
   <si>
-    <t>Cotizacion</t>
-  </si>
-  <si>
     <t>Status Resumido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Porcentual </t>
-  </si>
-  <si>
-    <t>Chance Venta</t>
-  </si>
-  <si>
-    <t>Numero</t>
   </si>
   <si>
     <t>Unidad</t>
   </si>
   <si>
-    <t>Cantid</t>
-  </si>
-  <si>
     <t>Valor + IGV</t>
-  </si>
-  <si>
-    <t>Previsto</t>
-  </si>
-  <si>
-    <t>Mes / Año</t>
-  </si>
-  <si>
-    <t>Resumen Prospeccion y Proyeccion - 2026  -  Compromisos</t>
-  </si>
-  <si>
-    <t>Fecha:</t>
-  </si>
-  <si>
-    <t>Nombre</t>
   </si>
   <si>
     <t>No. Contacto</t>
   </si>
   <si>
     <t>CODIGO-RESPONSABLE</t>
+  </si>
+  <si>
+    <t>N° Cotización</t>
+  </si>
+  <si>
+    <t>Cantidad</t>
+  </si>
+  <si>
+    <t>Chance de Venta</t>
+  </si>
+  <si>
+    <t>Mes Previsto</t>
   </si>
 </sst>
 </file>
@@ -91,7 +70,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;S/&quot;\ #,##0.00"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -108,20 +87,6 @@
     <font>
       <b/>
       <sz val="12"/>
-      <color theme="0"/>
-      <name val="Arial Nova"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="0"/>
-      <name val="Arial Nova"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="Arial Nova"/>
       <family val="2"/>
@@ -147,15 +112,8 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial Nova"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -165,18 +123,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -207,37 +153,34 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -248,18 +191,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -576,139 +507,122 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1E2E3C4-889B-4AB8-83D6-A2E78CADF733}">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:L68"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="51.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.28515625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="14.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="17.28515625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="18.7109375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="89.28515625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="17.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="48.42578125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="40.28515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="15.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="28.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="18" x14ac:dyDescent="0.25">
-      <c r="A1" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="K1" s="15">
-        <v>46121</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="13" t="s">
+      <c r="B1" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="13" t="s">
-        <v>1</v>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E1" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F1" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="16" t="s">
+      <c r="G1" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="16" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="13" t="s">
+      <c r="I1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="G3" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="13" t="s">
+      <c r="L1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="L3" s="16"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="5"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="5"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
-      <c r="C4" s="3"/>
+      <c r="C4" s="7"/>
       <c r="D4" s="3"/>
       <c r="E4" s="2"/>
       <c r="F4" s="2"/>
       <c r="G4" s="2"/>
       <c r="H4" s="4"/>
       <c r="I4" s="2"/>
-      <c r="J4" s="5"/>
+      <c r="J4" s="8"/>
       <c r="K4" s="6"/>
       <c r="L4" s="6"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="3"/>
+      <c r="C5" s="7"/>
       <c r="D5" s="3"/>
       <c r="E5" s="2"/>
       <c r="F5" s="2"/>
       <c r="G5" s="2"/>
       <c r="H5" s="4"/>
       <c r="I5" s="2"/>
-      <c r="J5" s="5"/>
+      <c r="J5" s="8"/>
       <c r="K5" s="6"/>
       <c r="L5" s="6"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="2"/>
+      <c r="A6" s="10"/>
       <c r="B6" s="2"/>
-      <c r="C6" s="7"/>
+      <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="2"/>
       <c r="F6" s="2"/>
@@ -720,9 +634,9 @@
       <c r="L6" s="6"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="2"/>
+      <c r="A7" s="10"/>
       <c r="B7" s="2"/>
-      <c r="C7" s="7"/>
+      <c r="C7" s="3"/>
       <c r="D7" s="3"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -916,38 +830,38 @@
       <c r="L20" s="6"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="2"/>
-      <c r="C21" s="3"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
       <c r="D21" s="3"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="4"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="8"/>
-      <c r="K21" s="6"/>
-      <c r="L21" s="6"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
+      <c r="K21" s="9"/>
+      <c r="L21" s="9"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A22" s="10"/>
-      <c r="B22" s="2"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="4"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="8"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
+      <c r="K22" s="9"/>
+      <c r="L22" s="9"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="9"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
-      <c r="D23" s="3"/>
+      <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
@@ -957,14 +871,637 @@
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
     </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
+      <c r="K24" s="9"/>
+      <c r="L24" s="9"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
+      <c r="K25" s="9"/>
+      <c r="L25" s="9"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
+      <c r="K26" s="9"/>
+      <c r="L26" s="9"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
+      <c r="K27" s="9"/>
+      <c r="L27" s="9"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
+      <c r="K28" s="9"/>
+      <c r="L28" s="9"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
+      <c r="K29" s="9"/>
+      <c r="L29" s="9"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
+      <c r="K30" s="9"/>
+      <c r="L30" s="9"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
+      <c r="K31" s="9"/>
+      <c r="L31" s="9"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
+      <c r="K32" s="9"/>
+      <c r="L32" s="9"/>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
+      <c r="F33" s="9"/>
+      <c r="G33" s="9"/>
+      <c r="H33" s="9"/>
+      <c r="I33" s="9"/>
+      <c r="J33" s="9"/>
+      <c r="K33" s="9"/>
+      <c r="L33" s="9"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
+      <c r="F34" s="9"/>
+      <c r="G34" s="9"/>
+      <c r="H34" s="9"/>
+      <c r="I34" s="9"/>
+      <c r="J34" s="9"/>
+      <c r="K34" s="9"/>
+      <c r="L34" s="9"/>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
+      <c r="F35" s="9"/>
+      <c r="G35" s="9"/>
+      <c r="H35" s="9"/>
+      <c r="I35" s="9"/>
+      <c r="J35" s="9"/>
+      <c r="K35" s="9"/>
+      <c r="L35" s="9"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
+      <c r="F36" s="9"/>
+      <c r="G36" s="9"/>
+      <c r="H36" s="9"/>
+      <c r="I36" s="9"/>
+      <c r="J36" s="9"/>
+      <c r="K36" s="9"/>
+      <c r="L36" s="9"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
+      <c r="F37" s="9"/>
+      <c r="G37" s="9"/>
+      <c r="H37" s="9"/>
+      <c r="I37" s="9"/>
+      <c r="J37" s="9"/>
+      <c r="K37" s="9"/>
+      <c r="L37" s="9"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="9"/>
+      <c r="H38" s="9"/>
+      <c r="I38" s="9"/>
+      <c r="J38" s="9"/>
+      <c r="K38" s="9"/>
+      <c r="L38" s="9"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
+      <c r="F39" s="9"/>
+      <c r="G39" s="9"/>
+      <c r="H39" s="9"/>
+      <c r="I39" s="9"/>
+      <c r="J39" s="9"/>
+      <c r="K39" s="9"/>
+      <c r="L39" s="9"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="9"/>
+      <c r="L40" s="9"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="9"/>
+      <c r="H41" s="9"/>
+      <c r="I41" s="9"/>
+      <c r="J41" s="9"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="9"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A42" s="9"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="9"/>
+      <c r="G42" s="9"/>
+      <c r="H42" s="9"/>
+      <c r="I42" s="9"/>
+      <c r="J42" s="9"/>
+      <c r="K42" s="9"/>
+      <c r="L42" s="9"/>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A43" s="9"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
+      <c r="H43" s="9"/>
+      <c r="I43" s="9"/>
+      <c r="J43" s="9"/>
+      <c r="K43" s="9"/>
+      <c r="L43" s="9"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A44" s="9"/>
+      <c r="B44" s="9"/>
+      <c r="C44" s="9"/>
+      <c r="D44" s="9"/>
+      <c r="E44" s="9"/>
+      <c r="F44" s="9"/>
+      <c r="G44" s="9"/>
+      <c r="H44" s="9"/>
+      <c r="I44" s="9"/>
+      <c r="J44" s="9"/>
+      <c r="K44" s="9"/>
+      <c r="L44" s="9"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A45" s="9"/>
+      <c r="B45" s="9"/>
+      <c r="C45" s="9"/>
+      <c r="D45" s="9"/>
+      <c r="E45" s="9"/>
+      <c r="F45" s="9"/>
+      <c r="G45" s="9"/>
+      <c r="H45" s="9"/>
+      <c r="I45" s="9"/>
+      <c r="J45" s="9"/>
+      <c r="K45" s="9"/>
+      <c r="L45" s="9"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A46" s="9"/>
+      <c r="B46" s="9"/>
+      <c r="C46" s="9"/>
+      <c r="D46" s="9"/>
+      <c r="E46" s="9"/>
+      <c r="F46" s="9"/>
+      <c r="G46" s="9"/>
+      <c r="H46" s="9"/>
+      <c r="I46" s="9"/>
+      <c r="J46" s="9"/>
+      <c r="K46" s="9"/>
+      <c r="L46" s="9"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A47" s="9"/>
+      <c r="B47" s="9"/>
+      <c r="C47" s="9"/>
+      <c r="D47" s="9"/>
+      <c r="E47" s="9"/>
+      <c r="F47" s="9"/>
+      <c r="G47" s="9"/>
+      <c r="H47" s="9"/>
+      <c r="I47" s="9"/>
+      <c r="J47" s="9"/>
+      <c r="K47" s="9"/>
+      <c r="L47" s="9"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A48" s="9"/>
+      <c r="B48" s="9"/>
+      <c r="C48" s="9"/>
+      <c r="D48" s="9"/>
+      <c r="E48" s="9"/>
+      <c r="F48" s="9"/>
+      <c r="G48" s="9"/>
+      <c r="H48" s="9"/>
+      <c r="I48" s="9"/>
+      <c r="J48" s="9"/>
+      <c r="K48" s="9"/>
+      <c r="L48" s="9"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A49" s="9"/>
+      <c r="B49" s="9"/>
+      <c r="C49" s="9"/>
+      <c r="D49" s="9"/>
+      <c r="E49" s="9"/>
+      <c r="F49" s="9"/>
+      <c r="G49" s="9"/>
+      <c r="H49" s="9"/>
+      <c r="I49" s="9"/>
+      <c r="J49" s="9"/>
+      <c r="K49" s="9"/>
+      <c r="L49" s="9"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A50" s="9"/>
+      <c r="B50" s="9"/>
+      <c r="C50" s="9"/>
+      <c r="D50" s="9"/>
+      <c r="E50" s="9"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="9"/>
+      <c r="K50" s="9"/>
+      <c r="L50" s="9"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A51" s="9"/>
+      <c r="B51" s="9"/>
+      <c r="C51" s="9"/>
+      <c r="D51" s="9"/>
+      <c r="E51" s="9"/>
+      <c r="F51" s="9"/>
+      <c r="G51" s="9"/>
+      <c r="H51" s="9"/>
+      <c r="I51" s="9"/>
+      <c r="J51" s="9"/>
+      <c r="K51" s="9"/>
+      <c r="L51" s="9"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A52" s="9"/>
+      <c r="B52" s="9"/>
+      <c r="C52" s="9"/>
+      <c r="D52" s="9"/>
+      <c r="E52" s="9"/>
+      <c r="F52" s="9"/>
+      <c r="G52" s="9"/>
+      <c r="H52" s="9"/>
+      <c r="I52" s="9"/>
+      <c r="J52" s="9"/>
+      <c r="K52" s="9"/>
+      <c r="L52" s="9"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="9"/>
+      <c r="B53" s="9"/>
+      <c r="C53" s="9"/>
+      <c r="D53" s="9"/>
+      <c r="E53" s="9"/>
+      <c r="F53" s="9"/>
+      <c r="G53" s="9"/>
+      <c r="H53" s="9"/>
+      <c r="I53" s="9"/>
+      <c r="J53" s="9"/>
+      <c r="K53" s="9"/>
+      <c r="L53" s="9"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A54" s="9"/>
+      <c r="B54" s="9"/>
+      <c r="C54" s="9"/>
+      <c r="D54" s="9"/>
+      <c r="E54" s="9"/>
+      <c r="F54" s="9"/>
+      <c r="G54" s="9"/>
+      <c r="H54" s="9"/>
+      <c r="I54" s="9"/>
+      <c r="J54" s="9"/>
+      <c r="K54" s="9"/>
+      <c r="L54" s="9"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A55" s="9"/>
+      <c r="B55" s="9"/>
+      <c r="C55" s="9"/>
+      <c r="D55" s="9"/>
+      <c r="E55" s="9"/>
+      <c r="F55" s="9"/>
+      <c r="G55" s="9"/>
+      <c r="H55" s="9"/>
+      <c r="I55" s="9"/>
+      <c r="J55" s="9"/>
+      <c r="K55" s="9"/>
+      <c r="L55" s="9"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A56" s="9"/>
+      <c r="B56" s="9"/>
+      <c r="C56" s="9"/>
+      <c r="D56" s="9"/>
+      <c r="E56" s="9"/>
+      <c r="F56" s="9"/>
+      <c r="G56" s="9"/>
+      <c r="H56" s="9"/>
+      <c r="I56" s="9"/>
+      <c r="J56" s="9"/>
+      <c r="K56" s="9"/>
+      <c r="L56" s="9"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A57" s="9"/>
+      <c r="B57" s="9"/>
+      <c r="C57" s="9"/>
+      <c r="D57" s="9"/>
+      <c r="E57" s="9"/>
+      <c r="F57" s="9"/>
+      <c r="G57" s="9"/>
+      <c r="H57" s="9"/>
+      <c r="I57" s="9"/>
+      <c r="J57" s="9"/>
+      <c r="K57" s="9"/>
+      <c r="L57" s="9"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A58" s="9"/>
+      <c r="B58" s="9"/>
+      <c r="C58" s="9"/>
+      <c r="D58" s="9"/>
+      <c r="E58" s="9"/>
+      <c r="F58" s="9"/>
+      <c r="G58" s="9"/>
+      <c r="H58" s="9"/>
+      <c r="I58" s="9"/>
+      <c r="J58" s="9"/>
+      <c r="K58" s="9"/>
+      <c r="L58" s="9"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+      <c r="C59" s="9"/>
+      <c r="D59" s="9"/>
+      <c r="E59" s="9"/>
+      <c r="F59" s="9"/>
+      <c r="G59" s="9"/>
+      <c r="H59" s="9"/>
+      <c r="I59" s="9"/>
+      <c r="J59" s="9"/>
+      <c r="K59" s="9"/>
+      <c r="L59" s="9"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A60" s="9"/>
+      <c r="B60" s="9"/>
+      <c r="C60" s="9"/>
+      <c r="D60" s="9"/>
+      <c r="E60" s="9"/>
+      <c r="F60" s="9"/>
+      <c r="G60" s="9"/>
+      <c r="H60" s="9"/>
+      <c r="I60" s="9"/>
+      <c r="J60" s="9"/>
+      <c r="K60" s="9"/>
+      <c r="L60" s="9"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A61" s="9"/>
+      <c r="B61" s="9"/>
+      <c r="C61" s="9"/>
+      <c r="D61" s="9"/>
+      <c r="E61" s="9"/>
+      <c r="F61" s="9"/>
+      <c r="G61" s="9"/>
+      <c r="H61" s="9"/>
+      <c r="I61" s="9"/>
+      <c r="J61" s="9"/>
+      <c r="K61" s="9"/>
+      <c r="L61" s="9"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A62" s="9"/>
+      <c r="B62" s="9"/>
+      <c r="C62" s="9"/>
+      <c r="D62" s="9"/>
+      <c r="E62" s="9"/>
+      <c r="F62" s="9"/>
+      <c r="G62" s="9"/>
+      <c r="H62" s="9"/>
+      <c r="I62" s="9"/>
+      <c r="J62" s="9"/>
+      <c r="K62" s="9"/>
+      <c r="L62" s="9"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A63" s="9"/>
+      <c r="B63" s="9"/>
+      <c r="C63" s="9"/>
+      <c r="D63" s="9"/>
+      <c r="E63" s="9"/>
+      <c r="F63" s="9"/>
+      <c r="G63" s="9"/>
+      <c r="H63" s="9"/>
+      <c r="I63" s="9"/>
+      <c r="J63" s="9"/>
+      <c r="K63" s="9"/>
+      <c r="L63" s="9"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A64" s="9"/>
+      <c r="B64" s="9"/>
+      <c r="C64" s="9"/>
+      <c r="D64" s="9"/>
+      <c r="E64" s="9"/>
+      <c r="F64" s="9"/>
+      <c r="G64" s="9"/>
+      <c r="H64" s="9"/>
+      <c r="I64" s="9"/>
+      <c r="J64" s="9"/>
+      <c r="K64" s="9"/>
+      <c r="L64" s="9"/>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A65" s="9"/>
+      <c r="B65" s="9"/>
+      <c r="C65" s="9"/>
+      <c r="D65" s="9"/>
+      <c r="E65" s="9"/>
+      <c r="F65" s="9"/>
+      <c r="G65" s="9"/>
+      <c r="H65" s="9"/>
+      <c r="I65" s="9"/>
+      <c r="J65" s="9"/>
+      <c r="K65" s="9"/>
+      <c r="L65" s="9"/>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A66" s="9"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="9"/>
+      <c r="D66" s="9"/>
+      <c r="E66" s="9"/>
+      <c r="F66" s="9"/>
+      <c r="G66" s="9"/>
+      <c r="H66" s="9"/>
+      <c r="I66" s="9"/>
+      <c r="J66" s="9"/>
+      <c r="K66" s="9"/>
+      <c r="L66" s="9"/>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A67" s="9"/>
+      <c r="B67" s="9"/>
+      <c r="C67" s="9"/>
+      <c r="D67" s="9"/>
+      <c r="E67" s="9"/>
+      <c r="F67" s="9"/>
+      <c r="G67" s="9"/>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9"/>
+      <c r="L67" s="9"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="9"/>
+      <c r="B68" s="9"/>
+      <c r="C68" s="9"/>
+      <c r="D68" s="9"/>
+      <c r="E68" s="9"/>
+      <c r="F68" s="9"/>
+      <c r="G68" s="9"/>
+      <c r="H68" s="9"/>
+      <c r="I68" s="9"/>
+      <c r="J68" s="9"/>
+      <c r="K68" s="9"/>
+      <c r="L68" s="9"/>
+    </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="I2:I3"/>
-    <mergeCell ref="E2:H2"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="L2:L3"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>